--- a/scenarios/02_mike_detector_engineer/2.2_1f_noise_corner_frequency/outputs/1f_noise_results.xlsx
+++ b/scenarios/02_mike_detector_engineer/2.2_1f_noise_corner_frequency/outputs/1f_noise_results.xlsx
@@ -515,19 +515,19 @@
         <v>357.63</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3088.13</v>
+        <v>2968.18</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3108.77</v>
+        <v>2989.64</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>39.1</v>
+        <v>37.58</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>39.36</v>
+        <v>37.85</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="5">
@@ -544,19 +544,19 @@
         <v>332.52</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3088.13</v>
+        <v>2968.18</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3105.98</v>
+        <v>2986.74</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>39.1</v>
+        <v>37.58</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>39.32</v>
+        <v>37.81</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         <v>305.36</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>3088.13</v>
+        <v>2968.18</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3103.19</v>
+        <v>2983.84</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>39.1</v>
+        <v>37.58</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>39.29</v>
+        <v>37.78</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
         <v>26.65</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>45.9</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="5">
@@ -666,86 +666,70 @@
         <v>25.74</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>42.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>nearfield_shot</t>
+          <t>quantization</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>852.33</v>
+        <v>352.18</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>10.79</v>
+        <v>4.46</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>quantization</t>
+          <t>read_noise</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>352.18</v>
+        <v>350</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>read_noise</t>
+          <t>flicker_1f</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>350</v>
+        <v>332.52</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.43</v>
+        <v>4.21</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>flicker_1f</t>
+          <t>dark_shot</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>332.52</v>
+        <v>7.07</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4.21</v>
+        <v>0.09</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>dark_shot</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -815,10 +799,10 @@
         <v>5.84</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3122.41</v>
+        <v>3003.83</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>39.53</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="5">
@@ -832,10 +816,10 @@
         <v>5.8</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3121.91</v>
+        <v>3003.3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>39.53</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="6">
@@ -849,10 +833,10 @@
         <v>5.75</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3121.4</v>
+        <v>3002.77</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>39.52</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="7">
@@ -866,10 +850,10 @@
         <v>5.71</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3120.89</v>
+        <v>3002.25</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>39.51</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="8">
@@ -883,10 +867,10 @@
         <v>5.67</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3120.38</v>
+        <v>3001.72</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>39.51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -900,10 +884,10 @@
         <v>5.62</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3119.87</v>
+        <v>3001.19</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>39.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -917,10 +901,10 @@
         <v>5.58</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3119.37</v>
+        <v>3000.66</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>39.49</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="11">
@@ -934,10 +918,10 @@
         <v>5.53</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3118.86</v>
+        <v>3000.13</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>39.49</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="12">
@@ -951,10 +935,10 @@
         <v>5.48</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3118.35</v>
+        <v>2999.61</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>39.48</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="13">
@@ -968,10 +952,10 @@
         <v>5.44</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3117.84</v>
+        <v>2999.08</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>39.47</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="14">
@@ -985,10 +969,10 @@
         <v>5.39</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3117.33</v>
+        <v>2998.55</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>39.47</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="15">
@@ -1002,10 +986,10 @@
         <v>5.34</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3116.82</v>
+        <v>2998.02</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>39.46</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="16">
@@ -1019,10 +1003,10 @@
         <v>5.29</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3116.31</v>
+        <v>2997.49</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>39.45</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="17">
@@ -1036,10 +1020,10 @@
         <v>5.25</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3115.81</v>
+        <v>2996.96</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>39.45</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="18">
@@ -1053,10 +1037,10 @@
         <v>5.2</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>3115.3</v>
+        <v>2996.43</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>39.44</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="19">
@@ -1070,10 +1054,10 @@
         <v>5.15</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3114.79</v>
+        <v>2995.9</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>39.44</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="20">
@@ -1087,10 +1071,10 @@
         <v>5.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3114.28</v>
+        <v>2995.37</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>39.43</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="21">
@@ -1104,10 +1088,10 @@
         <v>5.05</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>3113.77</v>
+        <v>2994.84</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>39.42</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="22">
@@ -1121,10 +1105,10 @@
         <v>5</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3113.26</v>
+        <v>2994.32</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>39.42</v>
+        <v>37.91</v>
       </c>
     </row>
     <row r="23">
@@ -1138,10 +1122,10 @@
         <v>4.95</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3112.75</v>
+        <v>2993.79</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>39.41</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="24">
@@ -1155,10 +1139,10 @@
         <v>4.9</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3112.24</v>
+        <v>2993.26</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>39.4</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="25">
@@ -1172,10 +1156,10 @@
         <v>4.84</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3111.73</v>
+        <v>2992.73</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>39.4</v>
+        <v>37.89</v>
       </c>
     </row>
     <row r="26">
@@ -1189,10 +1173,10 @@
         <v>4.79</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3111.22</v>
+        <v>2992.2</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>39.39</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="27">
@@ -1206,10 +1190,10 @@
         <v>4.74</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3110.71</v>
+        <v>2991.67</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>39.38</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="28">
@@ -1223,10 +1207,10 @@
         <v>4.68</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3110.2</v>
+        <v>2991.14</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>39.38</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="29">
@@ -1240,10 +1224,10 @@
         <v>4.63</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3109.69</v>
+        <v>2990.61</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>39.37</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="30">
@@ -1257,10 +1241,10 @@
         <v>4.57</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3109.18</v>
+        <v>2990.08</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>39.36</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="31">
@@ -1274,10 +1258,10 @@
         <v>4.52</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3108.67</v>
+        <v>2989.55</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>39.36</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="32">
@@ -1291,10 +1275,10 @@
         <v>4.46</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>3108.16</v>
+        <v>2989.02</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>39.35</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="33">
@@ -1308,10 +1292,10 @@
         <v>4.4</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>3107.65</v>
+        <v>2988.49</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>39.34</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="34">
@@ -1325,10 +1309,10 @@
         <v>4.35</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3107.14</v>
+        <v>2987.95</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>39.34</v>
+        <v>37.83</v>
       </c>
     </row>
     <row r="35">
@@ -1342,10 +1326,10 @@
         <v>4.29</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>3106.63</v>
+        <v>2987.42</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>39.33</v>
+        <v>37.82</v>
       </c>
     </row>
     <row r="36">
@@ -1359,10 +1343,10 @@
         <v>4.23</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3106.12</v>
+        <v>2986.89</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>39.33</v>
+        <v>37.82</v>
       </c>
     </row>
     <row r="37">
@@ -1376,10 +1360,10 @@
         <v>4.17</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>3105.61</v>
+        <v>2986.36</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>39.32</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="38">
@@ -1393,10 +1377,10 @@
         <v>4.1</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3105.1</v>
+        <v>2985.83</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>39.31</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="39">
@@ -1410,10 +1394,10 @@
         <v>4.04</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>3104.59</v>
+        <v>2985.3</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>39.31</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="40">
@@ -1427,10 +1411,10 @@
         <v>3.98</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>3104.08</v>
+        <v>2984.77</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>39.3</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="41">
@@ -1444,10 +1428,10 @@
         <v>3.91</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>3103.57</v>
+        <v>2984.24</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>39.29</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="42">
@@ -1461,10 +1445,10 @@
         <v>3.85</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3103.06</v>
+        <v>2983.71</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>39.29</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="43">
@@ -1478,10 +1462,10 @@
         <v>3.78</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>3102.55</v>
+        <v>2983.18</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>39.28</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="44">
@@ -1495,10 +1479,10 @@
         <v>3.71</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>3102.04</v>
+        <v>2982.64</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>39.27</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="45">
@@ -1512,10 +1496,10 @@
         <v>3.65</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>3101.53</v>
+        <v>2982.11</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>39.27</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="46">
@@ -1529,10 +1513,10 @@
         <v>3.58</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3101.01</v>
+        <v>2981.58</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>39.26</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="47">
@@ -1546,10 +1530,10 @@
         <v>3.5</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>3100.5</v>
+        <v>2981.05</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>39.25</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="48">
@@ -1563,10 +1547,10 @@
         <v>3.43</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3099.99</v>
+        <v>2980.52</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>39.25</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="49">
@@ -1580,10 +1564,10 @@
         <v>3.36</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3099.48</v>
+        <v>2979.99</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>39.24</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="50">
@@ -1597,10 +1581,10 @@
         <v>3.28</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>3098.97</v>
+        <v>2979.45</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>39.23</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="51">
@@ -1614,10 +1598,10 @@
         <v>3.2</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>3098.46</v>
+        <v>2978.92</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>39.23</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="52">
@@ -1631,10 +1615,10 @@
         <v>3.12</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>3097.95</v>
+        <v>2978.39</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>39.22</v>
+        <v>37.71</v>
       </c>
     </row>
     <row r="53">
@@ -1648,10 +1632,10 @@
         <v>3.04</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>3097.43</v>
+        <v>2977.86</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>39.22</v>
+        <v>37.7</v>
       </c>
     </row>
   </sheetData>
@@ -1827,7 +1811,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>39.1 mK</t>
+          <t>37.6 mK</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1823,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>39.3 mK</t>
+          <t>37.8 mK</t>
         </is>
       </c>
     </row>
